--- a/public/templates/請求書振替.xlsx
+++ b/public/templates/請求書振替.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/アプリ用テンプレ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{3DB82A3E-4CBD-47EB-9DB0-79D45A52FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AEF696-6945-4EC0-BCAE-4885A2D816AC}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{3DB82A3E-4CBD-47EB-9DB0-79D45A52FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFF1FC0-5180-4C33-8CE5-FD7653437610}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5209DA7A-5152-4F99-B3B1-55AC7DC7D125}"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <r>
       <t>請求書</t>
@@ -321,42 +321,6 @@
     <t>但:</t>
     <rPh sb="0" eb="1">
       <t>タダ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>任意代理人　月額管理 金銭管理　郵便管理</t>
-    <rPh sb="11" eb="13">
-      <t>キンセン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ユウビン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有料老人ホーム　サンライフ東駅</t>
-    <rPh sb="0" eb="4">
-      <t>ユウリョウロウジン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒガシエキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>齋藤俊子</t>
-    <rPh sb="0" eb="2">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トシコ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -1675,9 +1639,7 @@
       <c r="F2" s="37"/>
       <c r="G2" s="38"/>
       <c r="H2" s="39"/>
-      <c r="I2" s="19" t="s">
-        <v>28</v>
-      </c>
+      <c r="I2" s="19"/>
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
       <c r="L2" s="41"/>
@@ -1688,7 +1650,7 @@
     </row>
     <row r="3" spans="1:20" ht="21.75" customHeight="1">
       <c r="A3" s="42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
@@ -1708,7 +1670,7 @@
     </row>
     <row r="4" spans="1:20" ht="14.25" customHeight="1">
       <c r="A4" s="42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -1728,7 +1690,7 @@
     </row>
     <row r="5" spans="1:20" ht="41.25" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -1737,18 +1699,16 @@
       <c r="F5" s="47"/>
       <c r="G5" s="47"/>
       <c r="H5" s="45"/>
-      <c r="I5" s="32" t="s">
-        <v>29</v>
-      </c>
+      <c r="I5" s="32"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48"/>
       <c r="L5" s="48"/>
       <c r="M5" s="49" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N5" s="49">
         <f>I13</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" s="50" t="s">
         <v>1</v>
@@ -1858,17 +1818,15 @@
       <c r="F11" s="68"/>
       <c r="G11" s="54"/>
       <c r="H11" s="54"/>
-      <c r="I11" s="117" t="str">
+      <c r="I11" s="117">
         <f>I5</f>
-        <v>齋藤俊子</v>
+        <v>0</v>
       </c>
       <c r="J11" s="69"/>
       <c r="K11" s="69"/>
       <c r="L11" s="69"/>
       <c r="M11" s="69"/>
-      <c r="N11" s="18">
-        <v>46204</v>
-      </c>
+      <c r="N11" s="18"/>
       <c r="O11" s="70"/>
     </row>
     <row r="12" spans="1:20" ht="10.5" customHeight="1">
@@ -1904,9 +1862,7 @@
       <c r="H13" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="3">
-        <v>6</v>
-      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="76" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2112,7 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E25" s="81"/>
       <c r="F25" s="81"/>
@@ -2177,9 +2133,7 @@
       <c r="A26" s="22"/>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
-      <c r="D26" s="27" t="s">
-        <v>27</v>
-      </c>
+      <c r="D26" s="27"/>
       <c r="E26" s="81"/>
       <c r="F26" s="81"/>
       <c r="G26" s="81"/>
@@ -2350,7 +2304,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D35" s="102" t="s">
         <v>24</v>
@@ -2360,7 +2314,7 @@
       <c r="G35" s="104"/>
       <c r="H35" s="104"/>
       <c r="I35" s="119" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J35" s="119"/>
       <c r="K35" s="119"/>
@@ -2472,24 +2426,24 @@
         <v>26</v>
       </c>
       <c r="B40" s="111" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C40" s="112">
         <f>G13</f>
         <v>8</v>
       </c>
       <c r="D40" s="113" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E40" s="113">
         <f>I13</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F40" s="114" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G40" s="115" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H40" s="116"/>
       <c r="I40" s="119"/>
